--- a/product-definitions/spreadsheet/aerosol-extinction.xlsx
+++ b/product-definitions/spreadsheet/aerosol-extinction.xlsx
@@ -163,7 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -193,11 +193,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -247,29 +242,28 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1773,7 +1767,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="10"/>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1781,7 +1775,7 @@
       <c r="B19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1789,37 +1783,37 @@
       <c r="B20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="16">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C23" s="15"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19" t="s">
+      <c r="D23" s="18"/>
+      <c r="E23" s="18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="8" t="s">
         <v>24</v>
       </c>
@@ -1827,15 +1821,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="C25" s="10"/>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="8" t="s">
         <v>11</v>
       </c>
@@ -1843,7 +1837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="8" t="s">
         <v>13</v>
       </c>
@@ -1851,7 +1845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="8" t="s">
         <v>2</v>
       </c>
@@ -1859,58 +1853,58 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="10"/>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="16">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="B34" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="17" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C35" s="15"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19" t="s">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="8" t="s">
         <v>24</v>
       </c>
@@ -1918,16 +1912,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="C37" s="10"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C38" s="10"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="8" t="s">
         <v>11</v>
       </c>
@@ -1935,7 +1929,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="8" t="s">
         <v>13</v>
       </c>
@@ -1943,7 +1937,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="8" t="s">
         <v>2</v>
       </c>
@@ -1951,13 +1945,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="8" t="s">
         <v>15</v>
       </c>
@@ -1965,7 +1959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="12" t="s">
         <v>38</v>
       </c>
@@ -1973,21 +1967,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="19" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="B45" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47">
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="10"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="8" t="s">
         <v>11</v>
       </c>
@@ -1995,7 +1990,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="B49" s="8" t="s">
         <v>13</v>
       </c>
@@ -2003,7 +1998,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>2</v>
       </c>
@@ -2011,13 +2006,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="8" t="s">
         <v>15</v>
       </c>
@@ -2025,7 +2020,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="12" t="s">
         <v>38</v>
       </c>
@@ -2033,11 +2028,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="19" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="B54" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="19" t="s">
         <v>44</v>
       </c>
     </row>
